--- a/cleaned_sales_dataset.xlsx
+++ b/cleaned_sales_dataset.xlsx
@@ -8,19 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97D1CF6-FB14-4A53-AC58-CFC3DB286612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F79CAB-C787-4E3D-8009-9BE5E4029AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data set" sheetId="3" r:id="rId1"/>
     <sheet name="Data dictionary" sheetId="2" r:id="rId2"/>
     <sheet name="cleaned data set" sheetId="1" r:id="rId3"/>
+    <sheet name="EDA summary" sheetId="4" r:id="rId4"/>
+    <sheet name="Sales By City" sheetId="6" r:id="rId5"/>
+    <sheet name="Profit By Product" sheetId="8" r:id="rId6"/>
+    <sheet name="Profit vs Loss" sheetId="9" r:id="rId7"/>
+    <sheet name="Insights" sheetId="10" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'cleaned data set'!$A$1:$I$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="8" r:id="rId9"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +37,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="170">
   <si>
     <t>Order_ID</t>
   </si>
@@ -472,6 +479,81 @@
   </si>
   <si>
     <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Total Sales</t>
+  </si>
+  <si>
+    <t>Average Sales</t>
+  </si>
+  <si>
+    <t>Max Sales</t>
+  </si>
+  <si>
+    <t>Min Sales</t>
+  </si>
+  <si>
+    <t>Total Profit</t>
+  </si>
+  <si>
+    <t>Average Profit</t>
+  </si>
+  <si>
+    <t>Max Profit</t>
+  </si>
+  <si>
+    <t>Min Profit</t>
+  </si>
+  <si>
+    <t>Total Quantity</t>
+  </si>
+  <si>
+    <t>Average Quantity</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Sales</t>
+  </si>
+  <si>
+    <t>loss</t>
+  </si>
+  <si>
+    <t>Sum of Profit</t>
+  </si>
+  <si>
+    <t>Count of Profit_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Key Insights</t>
+  </si>
+  <si>
+    <t>Mumbai generates the highest sales, while Chennai has the lowest</t>
+  </si>
+  <si>
+    <t>Headphones are the most profitable product, whereas Laptops generate the lowest profit</t>
+  </si>
+  <si>
+    <t>Out of 100 transactions, 71 are profitable and 29 result in losses</t>
+  </si>
+  <si>
+    <t>A significant portion of transactions are profitable, but losses still exist and need attention</t>
+  </si>
+  <si>
+    <t>Profitability varies across different products, indicating scope for optimization</t>
+  </si>
+  <si>
+    <t>Laptops may require pricing or cost optimization due to lower profitability</t>
   </si>
 </sst>
 </file>
@@ -482,7 +564,7 @@
     <numFmt numFmtId="164" formatCode="[$-14009]yyyy/mm/dd;@"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -493,6 +575,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -519,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -543,6 +633,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -558,6 +664,4614 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[cleaned_sales_dataset.xlsx]Sales By City!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sales By City'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sales By City'!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Mumbai</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Pune</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Delhi</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Bangalore</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Chennai</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sales By City'!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>665618.67999999982</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>623218.93000000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>529876.06999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>452534.51</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>428296.2099999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5CF3-411D-8F8B-1D5EA2CCF3BA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="933021279"/>
+        <c:axId val="933021759"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="933021279"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="933021759"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="933021759"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="933021279"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent2"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[cleaned_sales_dataset.xlsx]Profit By Product!Profit By Product</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Profit By Product'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Profit By Product'!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Headphones</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Camera</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Phone</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Tablet</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Laptop</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Profit By Product'!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>104633.26999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>102979.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>88978.81</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>66969.48</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>61602.640000000007</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D330-438E-ABDC-9B251288235A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="929502239"/>
+        <c:axId val="929503199"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="929502239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="929503199"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="929503199"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="929502239"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="accent4">
+            <a:tint val="50000"/>
+            <a:satMod val="300000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="35000">
+          <a:schemeClr val="accent4">
+            <a:tint val="37000"/>
+            <a:satMod val="300000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="accent4">
+            <a:tint val="15000"/>
+            <a:satMod val="350000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:lin ang="16200000" scaled="1"/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent4">
+          <a:shade val="95000"/>
+          <a:satMod val="105000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst>
+      <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+        <a:srgbClr val="000000">
+          <a:alpha val="38000"/>
+        </a:srgbClr>
+      </a:outerShdw>
+    </a:effectLst>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[cleaned_sales_dataset.xlsx]Profit vs Loss!Profit vs Loss</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Profit vs Loss'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Profit vs Loss'!$A$4:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Profit</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>loss</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Profit vs Loss'!$B$4:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D794-45BE-B8AA-D0520692DD40}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>91440</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9437F9D4-6C26-2522-160C-16F886E55E90}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0CB2EAF-7449-0829-8B18-CC9078A56808}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3157F599-9CDE-CEBD-16F0-175F221A00C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Admin" refreshedDate="46133.366096759259" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="100" xr:uid="{E5AA25C0-5FEB-455D-AD89-C962FAB2A55C}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:J101" sheet="cleaned data set"/>
+  </cacheSource>
+  <cacheFields count="10">
+    <cacheField name="Order_ID" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Customer_Name" numFmtId="49">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="City" numFmtId="49">
+      <sharedItems count="5">
+        <s v="Mumbai"/>
+        <s v="Pune"/>
+        <s v="Delhi"/>
+        <s v="Bangalore"/>
+        <s v="Chennai"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Order_Date" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-01-03T00:00:00" maxDate="2023-12-27T00:00:00"/>
+    </cacheField>
+    <cacheField name="Product" numFmtId="49">
+      <sharedItems count="5">
+        <s v="Phone"/>
+        <s v="Laptop"/>
+        <s v="Camera"/>
+        <s v="Headphones"/>
+        <s v="Tablet"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Category" numFmtId="49">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Sales" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1291.98" maxValue="49476.49" count="100">
+        <n v="13558.24"/>
+        <n v="49460.12"/>
+        <n v="42789.26"/>
+        <n v="47662.54"/>
+        <n v="38624.99"/>
+        <n v="16184.28"/>
+        <n v="36764.46"/>
+        <n v="22808.1"/>
+        <n v="26566.79"/>
+        <n v="35541.410000000003"/>
+        <n v="27997"/>
+        <n v="48039.93"/>
+        <n v="27619.439999999999"/>
+        <n v="5622.95"/>
+        <n v="3781.86"/>
+        <n v="9312.0400000000009"/>
+        <n v="34023.93"/>
+        <n v="2741.45"/>
+        <n v="8485.59"/>
+        <n v="32607.77"/>
+        <n v="32935.35"/>
+        <n v="28410.32"/>
+        <n v="36398.28"/>
+        <n v="34503.800000000003"/>
+        <n v="23931.49"/>
+        <n v="37148.74"/>
+        <n v="43210.37"/>
+        <n v="21055.360000000001"/>
+        <n v="43710.31"/>
+        <n v="4752.82"/>
+        <n v="27891.39"/>
+        <n v="35432.050000000003"/>
+        <n v="38101.79"/>
+        <n v="43140.78"/>
+        <n v="26574.57"/>
+        <n v="46529.16"/>
+        <n v="10443.450000000001"/>
+        <n v="36041.82"/>
+        <n v="26649.74"/>
+        <n v="5426.29"/>
+        <n v="30161.02"/>
+        <n v="17725.86"/>
+        <n v="43663.62"/>
+        <n v="38113.74"/>
+        <n v="33141.300000000003"/>
+        <n v="39231.08"/>
+        <n v="14791.63"/>
+        <n v="39757.56"/>
+        <n v="10737.16"/>
+        <n v="47223.1"/>
+        <n v="39576.89"/>
+        <n v="16093.96"/>
+        <n v="40876.85"/>
+        <n v="48219.03"/>
+        <n v="5091.95"/>
+        <n v="13517.77"/>
+        <n v="7002.69"/>
+        <n v="16617.55"/>
+        <n v="3651.67"/>
+        <n v="30642.82"/>
+        <n v="32084.58"/>
+        <n v="20872.66"/>
+        <n v="38445.49"/>
+        <n v="19590.55"/>
+        <n v="44815.64"/>
+        <n v="16702.009999999998"/>
+        <n v="8787.41"/>
+        <n v="34931.25"/>
+        <n v="20071.740000000002"/>
+        <n v="37600.86"/>
+        <n v="32724.35"/>
+        <n v="1291.98"/>
+        <n v="24204.21"/>
+        <n v="45883.43"/>
+        <n v="43947.1"/>
+        <n v="44765.02"/>
+        <n v="16705.29"/>
+        <n v="49476.49"/>
+        <n v="6150.04"/>
+        <n v="11954.08"/>
+        <n v="25145.61"/>
+        <n v="1880.72"/>
+        <n v="14410.44"/>
+        <n v="9479.0499999999993"/>
+        <n v="41028.720000000001"/>
+        <n v="8411.6200000000008"/>
+        <n v="22698.11"/>
+        <n v="32903.74"/>
+        <n v="39813.15"/>
+        <n v="16656.57"/>
+        <n v="3029.59"/>
+        <n v="35108.92"/>
+        <n v="26425.62"/>
+        <n v="41400.339999999997"/>
+        <n v="20277.55"/>
+        <n v="36985.81"/>
+        <n v="12930.8"/>
+        <n v="22458.66"/>
+        <n v="34617.9"/>
+        <n v="34560.019999999997"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Quantity" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
+    </cacheField>
+    <cacheField name="Profit" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-4991.33" maxValue="14892.65"/>
+    </cacheField>
+    <cacheField name="Profit_Type" numFmtId="49">
+      <sharedItems count="2">
+        <s v="Profit"/>
+        <s v="loss"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="100">
+  <r>
+    <s v="ORD001"/>
+    <s v="Amit"/>
+    <x v="0"/>
+    <d v="2023-11-11T00:00:00"/>
+    <x v="0"/>
+    <s v="Accessories"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="7724.71"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD007"/>
+    <s v="Amit"/>
+    <x v="1"/>
+    <d v="2023-08-06T00:00:00"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <x v="1"/>
+    <n v="5"/>
+    <n v="6154.45"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD014"/>
+    <s v="Amit"/>
+    <x v="0"/>
+    <d v="2023-12-15T00:00:00"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <x v="2"/>
+    <n v="1"/>
+    <n v="13061.46"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD015"/>
+    <s v="Amit"/>
+    <x v="2"/>
+    <d v="2023-10-07T00:00:00"/>
+    <x v="2"/>
+    <s v="Electronics"/>
+    <x v="3"/>
+    <n v="1"/>
+    <n v="14892.65"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD016"/>
+    <s v="Amit"/>
+    <x v="2"/>
+    <d v="2023-08-13T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="4"/>
+    <n v="3"/>
+    <n v="6970.81"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD017"/>
+    <s v="Amit"/>
+    <x v="3"/>
+    <d v="2023-08-25T00:00:00"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <x v="5"/>
+    <n v="4"/>
+    <n v="-410.99"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD028"/>
+    <s v="Amit"/>
+    <x v="0"/>
+    <d v="2023-10-21T00:00:00"/>
+    <x v="3"/>
+    <s v="Accessories"/>
+    <x v="6"/>
+    <n v="4"/>
+    <n v="6904.11"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD045"/>
+    <s v="Amit"/>
+    <x v="2"/>
+    <d v="2023-05-31T00:00:00"/>
+    <x v="0"/>
+    <s v="Accessories"/>
+    <x v="7"/>
+    <n v="1"/>
+    <n v="6439"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD051"/>
+    <s v="Amit"/>
+    <x v="1"/>
+    <d v="2023-02-11T00:00:00"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <x v="8"/>
+    <n v="2"/>
+    <n v="6290.13"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD052"/>
+    <s v="Amit"/>
+    <x v="2"/>
+    <d v="2023-03-21T00:00:00"/>
+    <x v="0"/>
+    <s v="Accessories"/>
+    <x v="9"/>
+    <n v="1"/>
+    <n v="11068.01"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD057"/>
+    <s v="Amit"/>
+    <x v="1"/>
+    <d v="2023-05-17T00:00:00"/>
+    <x v="4"/>
+    <s v="Accessories"/>
+    <x v="10"/>
+    <n v="2"/>
+    <n v="-1706.51"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD059"/>
+    <s v="Amit"/>
+    <x v="4"/>
+    <d v="2023-05-12T00:00:00"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <x v="11"/>
+    <n v="5"/>
+    <n v="10866.16"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD064"/>
+    <s v="Amit"/>
+    <x v="0"/>
+    <d v="2023-01-04T00:00:00"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <x v="12"/>
+    <n v="2"/>
+    <n v="2418.38"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD066"/>
+    <s v="Amit"/>
+    <x v="4"/>
+    <d v="2023-09-03T00:00:00"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <x v="13"/>
+    <n v="1"/>
+    <n v="10960.44"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD073"/>
+    <s v="Amit"/>
+    <x v="0"/>
+    <d v="2023-01-06T00:00:00"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <x v="14"/>
+    <n v="1"/>
+    <n v="7529.26"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD087"/>
+    <s v="Amit"/>
+    <x v="0"/>
+    <d v="2023-06-20T00:00:00"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <x v="15"/>
+    <n v="5"/>
+    <n v="4763.75"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD091"/>
+    <s v="Amit"/>
+    <x v="0"/>
+    <d v="2023-01-03T00:00:00"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <x v="16"/>
+    <n v="4"/>
+    <n v="3371.38"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD093"/>
+    <s v="Amit"/>
+    <x v="3"/>
+    <d v="2023-03-12T00:00:00"/>
+    <x v="3"/>
+    <s v="Accessories"/>
+    <x v="17"/>
+    <n v="1"/>
+    <n v="10981.62"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD099"/>
+    <s v="Amit"/>
+    <x v="3"/>
+    <d v="2023-10-07T00:00:00"/>
+    <x v="3"/>
+    <s v="Accessories"/>
+    <x v="18"/>
+    <n v="1"/>
+    <n v="-1138.8699999999999"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD100"/>
+    <s v="Amit"/>
+    <x v="0"/>
+    <d v="2023-04-12T00:00:00"/>
+    <x v="2"/>
+    <s v="Electronics"/>
+    <x v="19"/>
+    <n v="5"/>
+    <n v="13975.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD002"/>
+    <s v="John"/>
+    <x v="2"/>
+    <d v="2023-02-23T00:00:00"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <x v="20"/>
+    <n v="5"/>
+    <n v="3496.69"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD010"/>
+    <s v="John"/>
+    <x v="2"/>
+    <d v="2023-03-29T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="21"/>
+    <n v="3"/>
+    <n v="12619.5"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD030"/>
+    <s v="John"/>
+    <x v="3"/>
+    <d v="2023-01-29T00:00:00"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <x v="22"/>
+    <n v="3"/>
+    <n v="-3671.99"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD031"/>
+    <s v="John"/>
+    <x v="2"/>
+    <d v="2023-11-28T00:00:00"/>
+    <x v="4"/>
+    <s v="Accessories"/>
+    <x v="23"/>
+    <n v="5"/>
+    <n v="2874.45"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD035"/>
+    <s v="John"/>
+    <x v="2"/>
+    <d v="2023-12-01T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="24"/>
+    <n v="5"/>
+    <n v="4863.54"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD053"/>
+    <s v="John"/>
+    <x v="0"/>
+    <d v="2023-11-26T00:00:00"/>
+    <x v="2"/>
+    <s v="Electronics"/>
+    <x v="25"/>
+    <n v="5"/>
+    <n v="3841.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD063"/>
+    <s v="John"/>
+    <x v="3"/>
+    <d v="2023-07-31T00:00:00"/>
+    <x v="3"/>
+    <s v="Accessories"/>
+    <x v="26"/>
+    <n v="5"/>
+    <n v="-4204.3599999999997"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD067"/>
+    <s v="John"/>
+    <x v="1"/>
+    <d v="2023-08-10T00:00:00"/>
+    <x v="2"/>
+    <s v="Electronics"/>
+    <x v="27"/>
+    <n v="2"/>
+    <n v="10788.47"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD082"/>
+    <s v="John"/>
+    <x v="1"/>
+    <d v="2023-08-15T00:00:00"/>
+    <x v="1"/>
+    <s v="Electronics"/>
+    <x v="28"/>
+    <n v="1"/>
+    <n v="9022.42"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD092"/>
+    <s v="John"/>
+    <x v="0"/>
+    <d v="2023-06-28T00:00:00"/>
+    <x v="0"/>
+    <s v="Accessories"/>
+    <x v="29"/>
+    <n v="3"/>
+    <n v="-2240.9899999999998"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD097"/>
+    <s v="John"/>
+    <x v="3"/>
+    <d v="2023-09-04T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="30"/>
+    <n v="4"/>
+    <n v="13923.16"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD011"/>
+    <s v="Neha"/>
+    <x v="1"/>
+    <d v="2023-01-08T00:00:00"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <x v="31"/>
+    <n v="1"/>
+    <n v="5253.51"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD012"/>
+    <s v="Neha"/>
+    <x v="2"/>
+    <d v="2023-03-10T00:00:00"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <x v="32"/>
+    <n v="2"/>
+    <n v="4491.3900000000003"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD032"/>
+    <s v="Neha"/>
+    <x v="1"/>
+    <d v="2023-09-20T00:00:00"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <x v="33"/>
+    <n v="5"/>
+    <n v="-598.62"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD033"/>
+    <s v="Neha"/>
+    <x v="1"/>
+    <d v="2023-09-26T00:00:00"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <x v="34"/>
+    <n v="2"/>
+    <n v="14513.15"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD047"/>
+    <s v="Neha"/>
+    <x v="1"/>
+    <d v="2023-10-26T00:00:00"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <x v="35"/>
+    <n v="1"/>
+    <n v="-1684.77"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD050"/>
+    <s v="Neha"/>
+    <x v="1"/>
+    <d v="2023-09-25T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="36"/>
+    <n v="1"/>
+    <n v="10050.33"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD055"/>
+    <s v="Neha"/>
+    <x v="1"/>
+    <d v="2023-08-28T00:00:00"/>
+    <x v="2"/>
+    <s v="Electronics"/>
+    <x v="37"/>
+    <n v="1"/>
+    <n v="13403.94"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD061"/>
+    <s v="Neha"/>
+    <x v="1"/>
+    <d v="2023-06-21T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="38"/>
+    <n v="2"/>
+    <n v="8660.14"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD062"/>
+    <s v="Neha"/>
+    <x v="3"/>
+    <d v="2023-11-16T00:00:00"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <x v="39"/>
+    <n v="4"/>
+    <n v="-492.05"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD077"/>
+    <s v="Neha"/>
+    <x v="4"/>
+    <d v="2023-09-24T00:00:00"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <x v="40"/>
+    <n v="4"/>
+    <n v="10914.03"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD081"/>
+    <s v="Neha"/>
+    <x v="3"/>
+    <d v="2023-01-17T00:00:00"/>
+    <x v="2"/>
+    <s v="Electronics"/>
+    <x v="41"/>
+    <n v="1"/>
+    <n v="9885.76"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD085"/>
+    <s v="Neha"/>
+    <x v="3"/>
+    <d v="2023-01-23T00:00:00"/>
+    <x v="1"/>
+    <s v="Electronics"/>
+    <x v="42"/>
+    <n v="2"/>
+    <n v="2424.29"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD086"/>
+    <s v="Neha"/>
+    <x v="0"/>
+    <d v="2023-08-07T00:00:00"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <x v="43"/>
+    <n v="2"/>
+    <n v="-980.23"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD003"/>
+    <s v="Priya"/>
+    <x v="3"/>
+    <d v="2023-11-18T00:00:00"/>
+    <x v="0"/>
+    <s v="Accessories"/>
+    <x v="44"/>
+    <n v="2"/>
+    <n v="141.78"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD008"/>
+    <s v="Priya"/>
+    <x v="0"/>
+    <d v="2023-06-19T00:00:00"/>
+    <x v="2"/>
+    <s v="Electronics"/>
+    <x v="45"/>
+    <n v="2"/>
+    <n v="288.77999999999997"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD018"/>
+    <s v="Priya"/>
+    <x v="2"/>
+    <d v="2023-06-19T00:00:00"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <x v="46"/>
+    <n v="1"/>
+    <n v="8843.41"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD019"/>
+    <s v="Priya"/>
+    <x v="1"/>
+    <d v="2023-05-09T00:00:00"/>
+    <x v="2"/>
+    <s v="Electronics"/>
+    <x v="47"/>
+    <n v="4"/>
+    <n v="2719.16"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD020"/>
+    <s v="Priya"/>
+    <x v="0"/>
+    <d v="2023-01-19T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="48"/>
+    <n v="1"/>
+    <n v="-4088.12"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD021"/>
+    <s v="Priya"/>
+    <x v="4"/>
+    <d v="2023-01-16T00:00:00"/>
+    <x v="4"/>
+    <s v="Accessories"/>
+    <x v="49"/>
+    <n v="5"/>
+    <n v="14838.68"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD025"/>
+    <s v="Priya"/>
+    <x v="1"/>
+    <d v="2023-12-19T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="50"/>
+    <n v="4"/>
+    <n v="671.99"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD029"/>
+    <s v="Priya"/>
+    <x v="1"/>
+    <d v="2023-12-26T00:00:00"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <x v="51"/>
+    <n v="5"/>
+    <n v="-964.78"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD034"/>
+    <s v="Priya"/>
+    <x v="0"/>
+    <d v="2023-11-29T00:00:00"/>
+    <x v="3"/>
+    <s v="Accessories"/>
+    <x v="52"/>
+    <n v="2"/>
+    <n v="663.53"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD036"/>
+    <s v="Priya"/>
+    <x v="1"/>
+    <d v="2023-02-13T00:00:00"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <x v="53"/>
+    <n v="4"/>
+    <n v="7607.86"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD039"/>
+    <s v="Priya"/>
+    <x v="1"/>
+    <d v="2023-07-26T00:00:00"/>
+    <x v="4"/>
+    <s v="Accessories"/>
+    <x v="54"/>
+    <n v="1"/>
+    <n v="-1812.15"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD044"/>
+    <s v="Priya"/>
+    <x v="4"/>
+    <d v="2023-02-21T00:00:00"/>
+    <x v="4"/>
+    <s v="Accessories"/>
+    <x v="55"/>
+    <n v="3"/>
+    <n v="-4455.57"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD048"/>
+    <s v="Priya"/>
+    <x v="2"/>
+    <d v="2023-08-17T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="56"/>
+    <n v="5"/>
+    <n v="5004.8500000000004"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD058"/>
+    <s v="Priya"/>
+    <x v="1"/>
+    <d v="2023-07-12T00:00:00"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <x v="57"/>
+    <n v="1"/>
+    <n v="-773.53"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD060"/>
+    <s v="Priya"/>
+    <x v="0"/>
+    <d v="2023-07-26T00:00:00"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <x v="58"/>
+    <n v="1"/>
+    <n v="5755.69"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD076"/>
+    <s v="Priya"/>
+    <x v="3"/>
+    <d v="2023-11-09T00:00:00"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <x v="59"/>
+    <n v="2"/>
+    <n v="5259.6"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD083"/>
+    <s v="Priya"/>
+    <x v="4"/>
+    <d v="2023-10-29T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="60"/>
+    <n v="1"/>
+    <n v="13187.62"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD004"/>
+    <s v="Rahul"/>
+    <x v="3"/>
+    <d v="2023-07-06T00:00:00"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <x v="61"/>
+    <n v="2"/>
+    <n v="3690.96"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD009"/>
+    <s v="Rahul"/>
+    <x v="0"/>
+    <d v="2023-04-14T00:00:00"/>
+    <x v="3"/>
+    <s v="Accessories"/>
+    <x v="62"/>
+    <n v="1"/>
+    <n v="8761.73"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD013"/>
+    <s v="Rahul"/>
+    <x v="4"/>
+    <d v="2023-01-06T00:00:00"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <x v="63"/>
+    <n v="4"/>
+    <n v="507.78"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD022"/>
+    <s v="Rahul"/>
+    <x v="2"/>
+    <d v="2023-01-30T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="64"/>
+    <n v="4"/>
+    <n v="-3796.16"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD027"/>
+    <s v="Rahul"/>
+    <x v="4"/>
+    <d v="2023-02-07T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="65"/>
+    <n v="1"/>
+    <n v="-998.51"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD038"/>
+    <s v="Rahul"/>
+    <x v="0"/>
+    <d v="2023-08-03T00:00:00"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <x v="66"/>
+    <n v="4"/>
+    <n v="6260.33"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD042"/>
+    <s v="Rahul"/>
+    <x v="0"/>
+    <d v="2023-09-02T00:00:00"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <x v="67"/>
+    <n v="5"/>
+    <n v="4206.03"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD049"/>
+    <s v="Rahul"/>
+    <x v="2"/>
+    <d v="2023-07-01T00:00:00"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <x v="68"/>
+    <n v="2"/>
+    <n v="7877.48"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD054"/>
+    <s v="Rahul"/>
+    <x v="4"/>
+    <d v="2023-06-02T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="69"/>
+    <n v="1"/>
+    <n v="7730.97"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD070"/>
+    <s v="Rahul"/>
+    <x v="3"/>
+    <d v="2023-06-11T00:00:00"/>
+    <x v="3"/>
+    <s v="Accessories"/>
+    <x v="70"/>
+    <n v="3"/>
+    <n v="6462.06"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD071"/>
+    <s v="Rahul"/>
+    <x v="2"/>
+    <d v="2023-05-17T00:00:00"/>
+    <x v="1"/>
+    <s v="Electronics"/>
+    <x v="71"/>
+    <n v="2"/>
+    <n v="-4282.45"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD072"/>
+    <s v="Rahul"/>
+    <x v="2"/>
+    <d v="2023-01-14T00:00:00"/>
+    <x v="4"/>
+    <s v="Accessories"/>
+    <x v="72"/>
+    <n v="5"/>
+    <n v="-315.37"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD075"/>
+    <s v="Rahul"/>
+    <x v="3"/>
+    <d v="2023-01-27T00:00:00"/>
+    <x v="4"/>
+    <s v="Accessories"/>
+    <x v="73"/>
+    <n v="3"/>
+    <n v="12086.86"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD080"/>
+    <s v="Rahul"/>
+    <x v="0"/>
+    <d v="2023-02-27T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="74"/>
+    <n v="4"/>
+    <n v="54.15"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD084"/>
+    <s v="Rahul"/>
+    <x v="2"/>
+    <d v="2023-04-02T00:00:00"/>
+    <x v="4"/>
+    <s v="Accessories"/>
+    <x v="75"/>
+    <n v="3"/>
+    <n v="-3737.42"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD090"/>
+    <s v="Rahul"/>
+    <x v="0"/>
+    <d v="2023-11-23T00:00:00"/>
+    <x v="2"/>
+    <s v="Electronics"/>
+    <x v="76"/>
+    <n v="1"/>
+    <n v="-4339.54"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD094"/>
+    <s v="Rahul"/>
+    <x v="4"/>
+    <d v="2023-12-20T00:00:00"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <x v="77"/>
+    <n v="5"/>
+    <n v="9597.2900000000009"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD098"/>
+    <s v="Rahul"/>
+    <x v="0"/>
+    <d v="2023-11-14T00:00:00"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <x v="78"/>
+    <n v="2"/>
+    <n v="-4329.6400000000003"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD005"/>
+    <s v="Sara"/>
+    <x v="3"/>
+    <d v="2023-04-19T00:00:00"/>
+    <x v="4"/>
+    <s v="Accessories"/>
+    <x v="79"/>
+    <n v="2"/>
+    <n v="-4142.6000000000004"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD006"/>
+    <s v="Sara"/>
+    <x v="1"/>
+    <d v="2023-11-21T00:00:00"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <x v="80"/>
+    <n v="3"/>
+    <n v="13285.73"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD023"/>
+    <s v="Sara"/>
+    <x v="2"/>
+    <d v="2023-05-01T00:00:00"/>
+    <x v="0"/>
+    <s v="Accessories"/>
+    <x v="81"/>
+    <n v="4"/>
+    <n v="-1657.73"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD024"/>
+    <s v="Sara"/>
+    <x v="0"/>
+    <d v="2023-07-06T00:00:00"/>
+    <x v="1"/>
+    <s v="Electronics"/>
+    <x v="82"/>
+    <n v="2"/>
+    <n v="8374.7199999999993"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD026"/>
+    <s v="Sara"/>
+    <x v="4"/>
+    <d v="2023-06-25T00:00:00"/>
+    <x v="1"/>
+    <s v="Electronics"/>
+    <x v="83"/>
+    <n v="1"/>
+    <n v="1252.26"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD037"/>
+    <s v="Sara"/>
+    <x v="3"/>
+    <d v="2023-01-24T00:00:00"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <x v="84"/>
+    <n v="5"/>
+    <n v="14737.67"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD040"/>
+    <s v="Sara"/>
+    <x v="0"/>
+    <d v="2023-04-02T00:00:00"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <x v="85"/>
+    <n v="1"/>
+    <n v="13771.52"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD041"/>
+    <s v="Sara"/>
+    <x v="2"/>
+    <d v="2023-04-27T00:00:00"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <x v="86"/>
+    <n v="2"/>
+    <n v="5326.06"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD043"/>
+    <s v="Sara"/>
+    <x v="2"/>
+    <d v="2023-11-28T00:00:00"/>
+    <x v="0"/>
+    <s v="Accessories"/>
+    <x v="87"/>
+    <n v="3"/>
+    <n v="150.97999999999999"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD046"/>
+    <s v="Sara"/>
+    <x v="0"/>
+    <d v="2023-12-03T00:00:00"/>
+    <x v="0"/>
+    <s v="Accessories"/>
+    <x v="88"/>
+    <n v="5"/>
+    <n v="-277.19"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD056"/>
+    <s v="Sara"/>
+    <x v="1"/>
+    <d v="2023-05-12T00:00:00"/>
+    <x v="3"/>
+    <s v="Accessories"/>
+    <x v="89"/>
+    <n v="2"/>
+    <n v="5609.43"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD065"/>
+    <s v="Sara"/>
+    <x v="0"/>
+    <d v="2023-03-13T00:00:00"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <x v="90"/>
+    <n v="3"/>
+    <n v="-4260.25"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD068"/>
+    <s v="Sara"/>
+    <x v="4"/>
+    <d v="2023-02-22T00:00:00"/>
+    <x v="4"/>
+    <s v="Accessories"/>
+    <x v="91"/>
+    <n v="4"/>
+    <n v="-4991.33"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD069"/>
+    <s v="Sara"/>
+    <x v="4"/>
+    <d v="2023-03-09T00:00:00"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <x v="92"/>
+    <n v="1"/>
+    <n v="295.29000000000002"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD074"/>
+    <s v="Sara"/>
+    <x v="0"/>
+    <d v="2023-10-22T00:00:00"/>
+    <x v="1"/>
+    <s v="Accessories"/>
+    <x v="93"/>
+    <n v="3"/>
+    <n v="9073.36"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD078"/>
+    <s v="Sara"/>
+    <x v="4"/>
+    <d v="2023-05-13T00:00:00"/>
+    <x v="4"/>
+    <s v="Accessories"/>
+    <x v="94"/>
+    <n v="4"/>
+    <n v="4185.3500000000004"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD079"/>
+    <s v="Sara"/>
+    <x v="4"/>
+    <d v="2023-02-27T00:00:00"/>
+    <x v="4"/>
+    <s v="Accessories"/>
+    <x v="95"/>
+    <n v="2"/>
+    <n v="1479.24"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD088"/>
+    <s v="Sara"/>
+    <x v="2"/>
+    <d v="2023-11-25T00:00:00"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <x v="96"/>
+    <n v="4"/>
+    <n v="491.54"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD089"/>
+    <s v="Sara"/>
+    <x v="1"/>
+    <d v="2023-04-11T00:00:00"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <x v="97"/>
+    <n v="2"/>
+    <n v="-4665.17"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ORD095"/>
+    <s v="Sara"/>
+    <x v="0"/>
+    <d v="2023-05-28T00:00:00"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <x v="98"/>
+    <n v="5"/>
+    <n v="5497.01"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ORD096"/>
+    <s v="Sara"/>
+    <x v="3"/>
+    <d v="2023-02-06T00:00:00"/>
+    <x v="2"/>
+    <s v="Accessories"/>
+    <x v="99"/>
+    <n v="1"/>
+    <n v="-4965.3"/>
+    <x v="1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4818936-6ED3-4486-B32F-2EF78461D564}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="6">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="2" showAll="0">
+      <items count="101">
+        <item x="71"/>
+        <item x="81"/>
+        <item x="17"/>
+        <item x="90"/>
+        <item x="58"/>
+        <item x="14"/>
+        <item x="29"/>
+        <item x="54"/>
+        <item x="39"/>
+        <item x="13"/>
+        <item x="78"/>
+        <item x="56"/>
+        <item x="85"/>
+        <item x="18"/>
+        <item x="66"/>
+        <item x="15"/>
+        <item x="83"/>
+        <item x="36"/>
+        <item x="48"/>
+        <item x="79"/>
+        <item x="96"/>
+        <item x="55"/>
+        <item x="0"/>
+        <item x="82"/>
+        <item x="46"/>
+        <item x="51"/>
+        <item x="5"/>
+        <item x="57"/>
+        <item x="89"/>
+        <item x="65"/>
+        <item x="76"/>
+        <item x="41"/>
+        <item x="63"/>
+        <item x="68"/>
+        <item x="94"/>
+        <item x="61"/>
+        <item x="27"/>
+        <item x="97"/>
+        <item x="86"/>
+        <item x="7"/>
+        <item x="24"/>
+        <item x="72"/>
+        <item x="80"/>
+        <item x="92"/>
+        <item x="8"/>
+        <item x="34"/>
+        <item x="38"/>
+        <item x="12"/>
+        <item x="30"/>
+        <item x="10"/>
+        <item x="21"/>
+        <item x="40"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="19"/>
+        <item x="70"/>
+        <item x="87"/>
+        <item x="20"/>
+        <item x="44"/>
+        <item x="16"/>
+        <item x="23"/>
+        <item x="99"/>
+        <item x="98"/>
+        <item x="67"/>
+        <item x="91"/>
+        <item x="31"/>
+        <item x="9"/>
+        <item x="37"/>
+        <item x="22"/>
+        <item x="6"/>
+        <item x="95"/>
+        <item x="25"/>
+        <item x="69"/>
+        <item x="32"/>
+        <item x="43"/>
+        <item x="62"/>
+        <item x="4"/>
+        <item x="45"/>
+        <item x="50"/>
+        <item x="47"/>
+        <item x="88"/>
+        <item x="52"/>
+        <item x="84"/>
+        <item x="93"/>
+        <item x="2"/>
+        <item x="33"/>
+        <item x="26"/>
+        <item x="42"/>
+        <item x="28"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="64"/>
+        <item x="73"/>
+        <item x="35"/>
+        <item x="49"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="53"/>
+        <item x="1"/>
+        <item x="77"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="6" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5DCEDAA7-F3A4-489F-98D1-5C341292442F}" name="Profit By Product" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="6">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField dataField="1" numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Profit" fld="8" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A3AE9303-AB9D-46BD-AB9C-C185D143BBBD}" name="Profit vs Loss" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Profit_Type" fld="9" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3949,8 +8663,9 @@
   <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="4"/>
-    <col min="2" max="3" width="8.88671875" style="7"/>
+    <col min="1" max="1" width="8.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="7"/>
     <col min="4" max="4" width="12.77734375" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.109375" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.44140625" style="7" bestFit="1" customWidth="1"/>
@@ -7297,4 +12012,344 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DC6A4-DC71-49F5-B62C-4DF87212E248}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" style="4" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="9">
+        <v>2699544.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="9">
+        <v>26995.439999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="9">
+        <v>49476.49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="9">
+        <v>1291.98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="9">
+        <v>425164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" s="9">
+        <v>4251.6400000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B8" s="9">
+        <v>14892.65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="9">
+        <v>-4991.33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="9">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2.77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A06B7C-E584-48DB-8974-7313756F596F}">
+  <dimension ref="A3:B9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="13">
+        <v>665618.67999999982</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="13">
+        <v>623218.93000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="13">
+        <v>529876.06999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="13">
+        <v>452534.51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="13">
+        <v>428296.2099999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="13">
+        <v>2699544.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58950FF4-1F2B-485C-9AE6-F5FEE0BCE380}">
+  <dimension ref="A3:B9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="13">
+        <v>104633.26999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="13">
+        <v>102979.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="13">
+        <v>88978.81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="13">
+        <v>66969.48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="13">
+        <v>61602.640000000007</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="13">
+        <v>425164</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F69181-3F09-4177-A6A0-2BBAFDA49ADB}">
+  <dimension ref="A3:B6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="14">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="14">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C61CBE80-FBAF-4DF3-9ECE-6522C7A35B86}">
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="79.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
+        <v>169</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>